--- a/Excel/FashionConfig.xlsx
+++ b/Excel/FashionConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2BCB6FA-74F6-44D7-9744-58FF92CA4708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC5EDE47-3CE0-4323-9ECE-27BE1FF5C8F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FashionProto" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="M3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="155">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -475,6 +475,132 @@
   </si>
   <si>
     <t>重击概率提升3%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name_EN</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Original Headpiece</t>
+  </si>
+  <si>
+    <t>Green hair accessory.</t>
+  </si>
+  <si>
+    <t>Blue Knight Headpiece</t>
+  </si>
+  <si>
+    <t>Excellence Guardian Hair</t>
+  </si>
+  <si>
+    <t>Black Gold Battle Blast</t>
+  </si>
+  <si>
+    <t>Original Eyes</t>
+  </si>
+  <si>
+    <t>Ocean's Eye</t>
+  </si>
+  <si>
+    <t>Knight's Eye</t>
+  </si>
+  <si>
+    <t>Black Gold Eyes</t>
+  </si>
+  <si>
+    <t>Original attire</t>
+  </si>
+  <si>
+    <t>Blue clothing</t>
+  </si>
+  <si>
+    <t>Blue Knight's Robe</t>
+  </si>
+  <si>
+    <t>Exalted Guardian Robe</t>
+  </si>
+  <si>
+    <t>Black Gold Battle Suit</t>
+  </si>
+  <si>
+    <t>Original hair</t>
+  </si>
+  <si>
+    <t>Blue hair</t>
+  </si>
+  <si>
+    <t>Witch's Magic Hat</t>
+  </si>
+  <si>
+    <t>Holy Priest's Crown</t>
+  </si>
+  <si>
+    <t>Magic uniform accessory</t>
+  </si>
+  <si>
+    <t>Witch's Eye</t>
+  </si>
+  <si>
+    <t>Divine Eyes</t>
+  </si>
+  <si>
+    <t>Magic Eye</t>
+  </si>
+  <si>
+    <t>Orange Armor</t>
+  </si>
+  <si>
+    <t>Witch's Magic Garment</t>
+  </si>
+  <si>
+    <t>Sacred Sacrificial Robe</t>
+  </si>
+  <si>
+    <t>Magic Uniform Shirt</t>
+  </si>
+  <si>
+    <t>PropertyDes_EN</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Critical Strike Chance Increased by 1%</t>
+  </si>
+  <si>
+    <t>Damage Mitigation +3%</t>
+  </si>
+  <si>
+    <t>Damage reduction is increased by 5%</t>
+  </si>
+  <si>
+    <t>Resilience probability increased by 2%</t>
+  </si>
+  <si>
+    <t>Heavy Strike Probability Increases by 2%</t>
+  </si>
+  <si>
+    <t>Increase the hit probability by 2%</t>
+  </si>
+  <si>
+    <t>Damage bonus increased by 3%</t>
+  </si>
+  <si>
+    <t>Damage bonus increased by 5%</t>
+  </si>
+  <si>
+    <t>Damage reduction increased by 4%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Increase critical hit rate by 3%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage bonus increased by 4%</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -5217,7 +5343,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -5238,6 +5364,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="1409" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1514">
     <cellStyle name="20% - 强调文字颜色 1 10" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
@@ -7081,28 +7208,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:M61"/>
+  <dimension ref="C1:O61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="10.875" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="21.375" customWidth="1"/>
     <col min="6" max="6" width="20.625" customWidth="1"/>
-    <col min="7" max="7" width="21.5" customWidth="1"/>
-    <col min="8" max="8" width="70" customWidth="1"/>
-    <col min="9" max="9" width="21.5" customWidth="1"/>
-    <col min="10" max="10" width="17.875" customWidth="1"/>
-    <col min="11" max="11" width="23.75" customWidth="1"/>
-    <col min="12" max="12" width="16.625" customWidth="1"/>
-    <col min="13" max="13" width="21.5" customWidth="1"/>
+    <col min="7" max="8" width="21.5" customWidth="1"/>
+    <col min="9" max="9" width="70" customWidth="1"/>
+    <col min="10" max="10" width="21.5" customWidth="1"/>
+    <col min="11" max="11" width="17.875" customWidth="1"/>
+    <col min="12" max="12" width="23.75" customWidth="1"/>
+    <col min="13" max="13" width="16.625" customWidth="1"/>
+    <col min="14" max="15" width="21.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:15" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H2" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="O2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -7119,25 +7254,31 @@
         <v>5</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="O3" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="4" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="2" t="s">
         <v>1</v>
       </c>
@@ -7154,25 +7295,31 @@
         <v>15</v>
       </c>
       <c r="H4" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="K4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="L4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="M4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="N4" s="4" t="s">
         <v>21</v>
       </c>
+      <c r="O4" s="4" t="s">
+        <v>143</v>
+      </c>
     </row>
-    <row r="5" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="2" t="s">
         <v>22</v>
       </c>
@@ -7195,19 +7342,25 @@
         <v>24</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="L5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="M5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="N5" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="O5" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="6" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="5">
         <v>10001000</v>
       </c>
@@ -7224,19 +7377,23 @@
         <v>27</v>
       </c>
       <c r="H6" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="J6" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="7"/>
       <c r="K6" s="7"/>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="7"/>
+      <c r="M6" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
     </row>
-    <row r="7" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="5">
         <v>10001010</v>
       </c>
@@ -7253,25 +7410,31 @@
         <v>31</v>
       </c>
       <c r="H7" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="J7" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="J7" s="7">
+      <c r="K7" s="7">
         <v>202103</v>
       </c>
-      <c r="K7" s="7">
+      <c r="L7" s="7">
         <v>100</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="M7" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M7" s="7" t="s">
+      <c r="N7" s="7" t="s">
         <v>34</v>
       </c>
+      <c r="O7" s="7" t="s">
+        <v>144</v>
+      </c>
     </row>
-    <row r="8" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C8" s="5">
         <v>10001020</v>
       </c>
@@ -7288,25 +7451,31 @@
         <v>35</v>
       </c>
       <c r="H8" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="J8" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="J8" s="7">
+      <c r="K8" s="7">
         <v>201003</v>
       </c>
-      <c r="K8" s="7">
+      <c r="L8" s="7">
         <v>300</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="M8" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M8" s="7" t="s">
+      <c r="N8" s="7" t="s">
         <v>38</v>
       </c>
+      <c r="O8" s="7" t="s">
+        <v>145</v>
+      </c>
     </row>
-    <row r="9" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C9" s="5">
         <v>10001030</v>
       </c>
@@ -7323,25 +7492,31 @@
         <v>39</v>
       </c>
       <c r="H9" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="J9" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="J9" s="7">
+      <c r="K9" s="7">
         <v>201003</v>
       </c>
-      <c r="K9" s="7">
+      <c r="L9" s="7">
         <v>500</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="M9" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M9" s="7" t="s">
+      <c r="N9" s="7" t="s">
         <v>42</v>
       </c>
+      <c r="O9" s="7" t="s">
+        <v>146</v>
+      </c>
     </row>
-    <row r="10" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C10" s="5">
         <v>10001040</v>
       </c>
@@ -7358,25 +7533,31 @@
         <v>106</v>
       </c>
       <c r="H10" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="J10" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="J10" s="7">
+      <c r="K10" s="7">
         <v>201003</v>
       </c>
-      <c r="K10" s="7">
+      <c r="L10" s="7">
         <v>400</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="M10" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M10" s="7" t="s">
+      <c r="N10" s="7" t="s">
         <v>112</v>
       </c>
+      <c r="O10" s="7" t="s">
+        <v>152</v>
+      </c>
     </row>
-    <row r="11" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C11" s="5">
         <v>10002000</v>
       </c>
@@ -7393,19 +7574,23 @@
         <v>43</v>
       </c>
       <c r="H11" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="I11" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="J11" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J11" s="7"/>
       <c r="K11" s="7"/>
-      <c r="L11" s="7" t="s">
+      <c r="L11" s="7"/>
+      <c r="M11" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
     </row>
-    <row r="12" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C12" s="5">
         <v>10002010</v>
       </c>
@@ -7422,25 +7607,31 @@
         <v>45</v>
       </c>
       <c r="H12" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="I12" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="J12" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="J12" s="7">
+      <c r="K12" s="7">
         <v>200403</v>
       </c>
-      <c r="K12" s="7">
+      <c r="L12" s="7">
         <v>200</v>
       </c>
-      <c r="L12" s="7" t="s">
+      <c r="M12" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M12" s="7" t="s">
+      <c r="N12" s="7" t="s">
         <v>48</v>
       </c>
+      <c r="O12" s="7" t="s">
+        <v>147</v>
+      </c>
     </row>
-    <row r="13" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C13" s="5">
         <v>10002020</v>
       </c>
@@ -7457,25 +7648,31 @@
         <v>49</v>
       </c>
       <c r="H13" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="J13" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="J13" s="7">
+      <c r="K13" s="7">
         <v>202103</v>
       </c>
-      <c r="K13" s="7">
+      <c r="L13" s="7">
         <v>200</v>
       </c>
-      <c r="L13" s="7" t="s">
+      <c r="M13" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M13" s="7" t="s">
+      <c r="N13" s="7" t="s">
         <v>52</v>
       </c>
+      <c r="O13" s="7" t="s">
+        <v>148</v>
+      </c>
     </row>
-    <row r="14" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C14" s="5">
         <v>10002030</v>
       </c>
@@ -7492,25 +7689,31 @@
         <v>105</v>
       </c>
       <c r="H14" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="I14" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="J14" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="J14" s="7">
+      <c r="K14" s="7">
         <v>202103</v>
       </c>
-      <c r="K14" s="7">
+      <c r="L14" s="7">
         <v>300</v>
       </c>
-      <c r="L14" s="7" t="s">
+      <c r="M14" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M14" s="7" t="s">
+      <c r="N14" s="7" t="s">
         <v>113</v>
       </c>
+      <c r="O14" s="7" t="s">
+        <v>153</v>
+      </c>
     </row>
-    <row r="15" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C15" s="5">
         <v>10003000</v>
       </c>
@@ -7527,19 +7730,23 @@
         <v>53</v>
       </c>
       <c r="H15" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="I15" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="J15" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J15" s="7"/>
       <c r="K15" s="7"/>
-      <c r="L15" s="7" t="s">
+      <c r="L15" s="7"/>
+      <c r="M15" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
     </row>
-    <row r="16" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C16" s="5">
         <v>10003010</v>
       </c>
@@ -7556,25 +7763,31 @@
         <v>56</v>
       </c>
       <c r="H16" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="I16" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="J16" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="J16" s="7">
+      <c r="K16" s="7">
         <v>200203</v>
       </c>
-      <c r="K16" s="7">
+      <c r="L16" s="7">
         <v>200</v>
       </c>
-      <c r="L16" s="7" t="s">
+      <c r="M16" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M16" s="7" t="s">
+      <c r="N16" s="7" t="s">
         <v>58</v>
       </c>
+      <c r="O16" s="7" t="s">
+        <v>149</v>
+      </c>
     </row>
-    <row r="17" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C17" s="5">
         <v>10003020</v>
       </c>
@@ -7591,25 +7804,31 @@
         <v>59</v>
       </c>
       <c r="H17" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="I17" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="I17" s="7" t="s">
+      <c r="J17" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="J17" s="7">
+      <c r="K17" s="7">
         <v>200903</v>
       </c>
-      <c r="K17" s="7">
+      <c r="L17" s="7">
         <v>300</v>
       </c>
-      <c r="L17" s="7" t="s">
+      <c r="M17" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M17" s="7" t="s">
+      <c r="N17" s="7" t="s">
         <v>62</v>
       </c>
+      <c r="O17" s="7" t="s">
+        <v>150</v>
+      </c>
     </row>
-    <row r="18" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C18" s="5">
         <v>10003030</v>
       </c>
@@ -7626,25 +7845,31 @@
         <v>63</v>
       </c>
       <c r="H18" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="I18" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="I18" s="7" t="s">
+      <c r="J18" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="J18" s="7">
+      <c r="K18" s="7">
         <v>200903</v>
       </c>
-      <c r="K18" s="7">
+      <c r="L18" s="7">
         <v>500</v>
       </c>
-      <c r="L18" s="7" t="s">
+      <c r="M18" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M18" s="7" t="s">
+      <c r="N18" s="7" t="s">
         <v>66</v>
       </c>
+      <c r="O18" s="7" t="s">
+        <v>151</v>
+      </c>
     </row>
-    <row r="19" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C19" s="5">
         <v>10003040</v>
       </c>
@@ -7661,25 +7886,31 @@
         <v>104</v>
       </c>
       <c r="H19" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I19" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="I19" s="7" t="s">
+      <c r="J19" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="J19" s="7">
+      <c r="K19" s="7">
         <v>200903</v>
       </c>
-      <c r="K19" s="7">
+      <c r="L19" s="7">
         <v>400</v>
       </c>
-      <c r="L19" s="7" t="s">
+      <c r="M19" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M19" s="7" t="s">
+      <c r="N19" s="7" t="s">
         <v>111</v>
       </c>
+      <c r="O19" s="7" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="20" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C20" s="5">
         <v>20001000</v>
       </c>
@@ -7696,19 +7927,23 @@
         <v>67</v>
       </c>
       <c r="H20" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="I20" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="I20" s="7" t="s">
+      <c r="J20" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J20" s="7"/>
       <c r="K20" s="7"/>
-      <c r="L20" s="7" t="s">
+      <c r="L20" s="7"/>
+      <c r="M20" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
     </row>
-    <row r="21" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C21" s="5">
         <v>20001010</v>
       </c>
@@ -7725,25 +7960,31 @@
         <v>70</v>
       </c>
       <c r="H21" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="I21" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="I21" s="7" t="s">
+      <c r="J21" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="J21" s="7">
+      <c r="K21" s="7">
         <v>202103</v>
       </c>
-      <c r="K21" s="7">
+      <c r="L21" s="7">
         <v>100</v>
       </c>
-      <c r="L21" s="7" t="s">
+      <c r="M21" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="M21" s="7" t="s">
+      <c r="N21" s="7" t="s">
         <v>34</v>
       </c>
+      <c r="O21" s="7" t="s">
+        <v>144</v>
+      </c>
     </row>
-    <row r="22" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C22" s="5">
         <v>20001020</v>
       </c>
@@ -7760,25 +8001,31 @@
         <v>72</v>
       </c>
       <c r="H22" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I22" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="I22" s="7" t="s">
+      <c r="J22" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="J22" s="7">
+      <c r="K22" s="7">
         <v>201003</v>
       </c>
-      <c r="K22" s="7">
+      <c r="L22" s="7">
         <v>300</v>
       </c>
-      <c r="L22" s="7" t="s">
+      <c r="M22" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="M22" s="7" t="s">
+      <c r="N22" s="7" t="s">
         <v>38</v>
       </c>
+      <c r="O22" s="7" t="s">
+        <v>145</v>
+      </c>
     </row>
-    <row r="23" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C23" s="5">
         <v>20001030</v>
       </c>
@@ -7795,25 +8042,31 @@
         <v>75</v>
       </c>
       <c r="H23" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="I23" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I23" s="7" t="s">
+      <c r="J23" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="J23" s="7">
+      <c r="K23" s="7">
         <v>201003</v>
       </c>
-      <c r="K23" s="7">
+      <c r="L23" s="7">
         <v>500</v>
       </c>
-      <c r="L23" s="7" t="s">
+      <c r="M23" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="M23" s="7" t="s">
+      <c r="N23" s="7" t="s">
         <v>42</v>
       </c>
+      <c r="O23" s="7" t="s">
+        <v>146</v>
+      </c>
     </row>
-    <row r="24" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C24" s="5">
         <v>20001040</v>
       </c>
@@ -7830,25 +8083,31 @@
         <v>95</v>
       </c>
       <c r="H24" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="I24" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="I24" s="7" t="s">
+      <c r="J24" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="J24" s="7">
+      <c r="K24" s="7">
         <v>201003</v>
       </c>
-      <c r="K24" s="7">
+      <c r="L24" s="7">
         <v>400</v>
       </c>
-      <c r="L24" s="7" t="s">
+      <c r="M24" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="M24" s="7" t="s">
+      <c r="N24" s="7" t="s">
         <v>112</v>
       </c>
+      <c r="O24" s="7" t="s">
+        <v>152</v>
+      </c>
     </row>
-    <row r="25" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C25" s="5">
         <v>20002000</v>
       </c>
@@ -7865,19 +8124,23 @@
         <v>43</v>
       </c>
       <c r="H25" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="I25" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I25" s="7" t="s">
+      <c r="J25" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J25" s="7"/>
       <c r="K25" s="7"/>
-      <c r="L25" s="7" t="s">
+      <c r="L25" s="7"/>
+      <c r="M25" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="7"/>
     </row>
-    <row r="26" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C26" s="5">
         <v>20002010</v>
       </c>
@@ -7894,25 +8157,31 @@
         <v>78</v>
       </c>
       <c r="H26" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="I26" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="I26" s="7" t="s">
+      <c r="J26" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="J26" s="7">
+      <c r="K26" s="7">
         <v>200403</v>
       </c>
-      <c r="K26" s="7">
+      <c r="L26" s="7">
         <v>200</v>
       </c>
-      <c r="L26" s="7" t="s">
+      <c r="M26" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M26" s="7" t="s">
+      <c r="N26" s="7" t="s">
         <v>48</v>
       </c>
+      <c r="O26" s="7" t="s">
+        <v>147</v>
+      </c>
     </row>
-    <row r="27" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C27" s="5">
         <v>20002020</v>
       </c>
@@ -7929,25 +8198,31 @@
         <v>80</v>
       </c>
       <c r="H27" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I27" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="I27" s="7" t="s">
+      <c r="J27" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="J27" s="7">
+      <c r="K27" s="7">
         <v>202103</v>
       </c>
-      <c r="K27" s="7">
+      <c r="L27" s="7">
         <v>200</v>
       </c>
-      <c r="L27" s="7" t="s">
+      <c r="M27" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M27" s="7" t="s">
+      <c r="N27" s="7" t="s">
         <v>52</v>
       </c>
+      <c r="O27" s="7" t="s">
+        <v>148</v>
+      </c>
     </row>
-    <row r="28" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C28" s="5">
         <v>20002030</v>
       </c>
@@ -7964,25 +8239,31 @@
         <v>98</v>
       </c>
       <c r="H28" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I28" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="I28" s="7" t="s">
+      <c r="J28" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="J28" s="7">
+      <c r="K28" s="7">
         <v>202103</v>
       </c>
-      <c r="K28" s="7">
+      <c r="L28" s="7">
         <v>300</v>
       </c>
-      <c r="L28" s="7" t="s">
+      <c r="M28" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M28" s="7" t="s">
+      <c r="N28" s="7" t="s">
         <v>113</v>
       </c>
+      <c r="O28" s="7" t="s">
+        <v>153</v>
+      </c>
     </row>
-    <row r="29" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C29" s="5">
         <v>20003000</v>
       </c>
@@ -7999,19 +8280,23 @@
         <v>53</v>
       </c>
       <c r="H29" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="I29" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="I29" s="7" t="s">
+      <c r="J29" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J29" s="7"/>
       <c r="K29" s="7"/>
-      <c r="L29" s="7" t="s">
+      <c r="L29" s="7"/>
+      <c r="M29" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
+      <c r="O29" s="7"/>
     </row>
-    <row r="30" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C30" s="5">
         <v>20003010</v>
       </c>
@@ -8028,25 +8313,31 @@
         <v>83</v>
       </c>
       <c r="H30" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="I30" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="I30" s="7" t="s">
+      <c r="J30" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="J30" s="7">
+      <c r="K30" s="7">
         <v>200203</v>
       </c>
-      <c r="K30" s="7">
+      <c r="L30" s="7">
         <v>200</v>
       </c>
-      <c r="L30" s="7" t="s">
+      <c r="M30" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M30" s="7" t="s">
+      <c r="N30" s="7" t="s">
         <v>58</v>
       </c>
+      <c r="O30" s="7" t="s">
+        <v>149</v>
+      </c>
     </row>
-    <row r="31" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C31" s="5">
         <v>20003020</v>
       </c>
@@ -8063,25 +8354,31 @@
         <v>85</v>
       </c>
       <c r="H31" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="I31" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="I31" s="7" t="s">
+      <c r="J31" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="J31" s="7">
+      <c r="K31" s="7">
         <v>200903</v>
       </c>
-      <c r="K31" s="7">
+      <c r="L31" s="7">
         <v>300</v>
       </c>
-      <c r="L31" s="7" t="s">
+      <c r="M31" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M31" s="7" t="s">
+      <c r="N31" s="7" t="s">
         <v>62</v>
       </c>
+      <c r="O31" s="7" t="s">
+        <v>150</v>
+      </c>
     </row>
-    <row r="32" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C32" s="5">
         <v>20003030</v>
       </c>
@@ -8098,25 +8395,31 @@
         <v>87</v>
       </c>
       <c r="H32" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="I32" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="I32" s="7" t="s">
+      <c r="J32" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="J32" s="7">
+      <c r="K32" s="7">
         <v>200903</v>
       </c>
-      <c r="K32" s="7">
+      <c r="L32" s="7">
         <v>500</v>
       </c>
-      <c r="L32" s="7" t="s">
+      <c r="M32" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M32" s="7" t="s">
+      <c r="N32" s="7" t="s">
         <v>66</v>
       </c>
+      <c r="O32" s="7" t="s">
+        <v>151</v>
+      </c>
     </row>
-    <row r="33" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C33" s="5">
         <v>20003040</v>
       </c>
@@ -8133,25 +8436,31 @@
         <v>99</v>
       </c>
       <c r="H33" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="I33" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I33" s="7" t="s">
+      <c r="J33" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="J33" s="7">
+      <c r="K33" s="7">
         <v>200903</v>
       </c>
-      <c r="K33" s="7">
+      <c r="L33" s="7">
         <v>400</v>
       </c>
-      <c r="L33" s="7" t="s">
+      <c r="M33" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M33" s="7" t="s">
+      <c r="N33" s="7" t="s">
         <v>111</v>
       </c>
+      <c r="O33" s="7" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="34" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C34" s="5">
         <v>30001000</v>
       </c>
@@ -8168,19 +8477,23 @@
         <v>27</v>
       </c>
       <c r="H34" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I34" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="I34" s="7" t="s">
+      <c r="J34" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J34" s="7"/>
       <c r="K34" s="7"/>
-      <c r="L34" s="7" t="s">
+      <c r="L34" s="7"/>
+      <c r="M34" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M34" s="7"/>
+      <c r="N34" s="7"/>
+      <c r="O34" s="7"/>
     </row>
-    <row r="35" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C35" s="5">
         <v>30001010</v>
       </c>
@@ -8197,25 +8510,31 @@
         <v>31</v>
       </c>
       <c r="H35" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="I35" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="I35" s="7" t="s">
+      <c r="J35" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="J35" s="7">
+      <c r="K35" s="7">
         <v>202103</v>
       </c>
-      <c r="K35" s="7">
+      <c r="L35" s="7">
         <v>100</v>
       </c>
-      <c r="L35" s="7" t="s">
+      <c r="M35" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M35" s="7" t="s">
+      <c r="N35" s="7" t="s">
         <v>34</v>
       </c>
+      <c r="O35" s="7" t="s">
+        <v>144</v>
+      </c>
     </row>
-    <row r="36" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C36" s="5">
         <v>30001020</v>
       </c>
@@ -8232,25 +8551,31 @@
         <v>35</v>
       </c>
       <c r="H36" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="I36" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="I36" s="7" t="s">
+      <c r="J36" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="J36" s="7">
+      <c r="K36" s="7">
         <v>201003</v>
       </c>
-      <c r="K36" s="7">
+      <c r="L36" s="7">
         <v>300</v>
       </c>
-      <c r="L36" s="7" t="s">
+      <c r="M36" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M36" s="7" t="s">
+      <c r="N36" s="7" t="s">
         <v>38</v>
       </c>
+      <c r="O36" s="7" t="s">
+        <v>145</v>
+      </c>
     </row>
-    <row r="37" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C37" s="5">
         <v>30001030</v>
       </c>
@@ -8267,25 +8592,31 @@
         <v>39</v>
       </c>
       <c r="H37" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="I37" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="I37" s="7" t="s">
+      <c r="J37" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="J37" s="7">
+      <c r="K37" s="7">
         <v>201003</v>
       </c>
-      <c r="K37" s="7">
+      <c r="L37" s="7">
         <v>500</v>
       </c>
-      <c r="L37" s="7" t="s">
+      <c r="M37" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M37" s="7" t="s">
+      <c r="N37" s="7" t="s">
         <v>42</v>
       </c>
+      <c r="O37" s="7" t="s">
+        <v>146</v>
+      </c>
     </row>
-    <row r="38" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C38" s="5">
         <v>30001040</v>
       </c>
@@ -8302,25 +8633,31 @@
         <v>106</v>
       </c>
       <c r="H38" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="I38" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="I38" s="7" t="s">
+      <c r="J38" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="J38" s="7">
+      <c r="K38" s="7">
         <v>201003</v>
       </c>
-      <c r="K38" s="7">
+      <c r="L38" s="7">
         <v>400</v>
       </c>
-      <c r="L38" s="7" t="s">
+      <c r="M38" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M38" s="7" t="s">
+      <c r="N38" s="7" t="s">
         <v>112</v>
       </c>
+      <c r="O38" s="7" t="s">
+        <v>152</v>
+      </c>
     </row>
-    <row r="39" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C39" s="5">
         <v>30002000</v>
       </c>
@@ -8337,19 +8674,23 @@
         <v>43</v>
       </c>
       <c r="H39" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="I39" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="I39" s="7" t="s">
+      <c r="J39" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J39" s="7"/>
       <c r="K39" s="7"/>
-      <c r="L39" s="7" t="s">
+      <c r="L39" s="7"/>
+      <c r="M39" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M39" s="7"/>
+      <c r="N39" s="7"/>
+      <c r="O39" s="7"/>
     </row>
-    <row r="40" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C40" s="5">
         <v>30002010</v>
       </c>
@@ -8366,25 +8707,31 @@
         <v>45</v>
       </c>
       <c r="H40" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="I40" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="I40" s="7" t="s">
+      <c r="J40" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="J40" s="7">
+      <c r="K40" s="7">
         <v>200403</v>
       </c>
-      <c r="K40" s="7">
+      <c r="L40" s="7">
         <v>200</v>
       </c>
-      <c r="L40" s="7" t="s">
+      <c r="M40" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M40" s="7" t="s">
+      <c r="N40" s="7" t="s">
         <v>48</v>
       </c>
+      <c r="O40" s="7" t="s">
+        <v>147</v>
+      </c>
     </row>
-    <row r="41" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C41" s="5">
         <v>30002020</v>
       </c>
@@ -8401,25 +8748,31 @@
         <v>49</v>
       </c>
       <c r="H41" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="I41" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="I41" s="7" t="s">
+      <c r="J41" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="J41" s="7">
+      <c r="K41" s="7">
         <v>202103</v>
       </c>
-      <c r="K41" s="7">
+      <c r="L41" s="7">
         <v>200</v>
       </c>
-      <c r="L41" s="7" t="s">
+      <c r="M41" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M41" s="7" t="s">
+      <c r="N41" s="7" t="s">
         <v>52</v>
       </c>
+      <c r="O41" s="7" t="s">
+        <v>148</v>
+      </c>
     </row>
-    <row r="42" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C42" s="5">
         <v>30002030</v>
       </c>
@@ -8436,25 +8789,31 @@
         <v>105</v>
       </c>
       <c r="H42" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="I42" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="I42" s="7" t="s">
+      <c r="J42" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="J42" s="7">
+      <c r="K42" s="7">
         <v>202103</v>
       </c>
-      <c r="K42" s="7">
+      <c r="L42" s="7">
         <v>300</v>
       </c>
-      <c r="L42" s="7" t="s">
+      <c r="M42" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M42" s="7" t="s">
+      <c r="N42" s="7" t="s">
         <v>114</v>
       </c>
+      <c r="O42" s="7" t="s">
+        <v>153</v>
+      </c>
     </row>
-    <row r="43" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C43" s="5">
         <v>30003000</v>
       </c>
@@ -8471,19 +8830,23 @@
         <v>53</v>
       </c>
       <c r="H43" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="I43" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="I43" s="7" t="s">
+      <c r="J43" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J43" s="7"/>
       <c r="K43" s="7"/>
-      <c r="L43" s="7" t="s">
+      <c r="L43" s="7"/>
+      <c r="M43" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M43" s="7"/>
+      <c r="N43" s="7"/>
+      <c r="O43" s="7"/>
     </row>
-    <row r="44" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C44" s="5">
         <v>30003010</v>
       </c>
@@ -8500,25 +8863,31 @@
         <v>56</v>
       </c>
       <c r="H44" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="I44" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="I44" s="7" t="s">
+      <c r="J44" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="J44" s="7">
+      <c r="K44" s="7">
         <v>200203</v>
       </c>
-      <c r="K44" s="7">
+      <c r="L44" s="7">
         <v>200</v>
       </c>
-      <c r="L44" s="7" t="s">
+      <c r="M44" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M44" s="7" t="s">
+      <c r="N44" s="7" t="s">
         <v>58</v>
       </c>
+      <c r="O44" s="7" t="s">
+        <v>149</v>
+      </c>
     </row>
-    <row r="45" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C45" s="5">
         <v>30003020</v>
       </c>
@@ -8535,25 +8904,31 @@
         <v>59</v>
       </c>
       <c r="H45" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="I45" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="I45" s="7" t="s">
+      <c r="J45" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="J45" s="7">
+      <c r="K45" s="7">
         <v>200903</v>
       </c>
-      <c r="K45" s="7">
+      <c r="L45" s="7">
         <v>300</v>
       </c>
-      <c r="L45" s="7" t="s">
+      <c r="M45" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M45" s="7" t="s">
+      <c r="N45" s="7" t="s">
         <v>62</v>
       </c>
+      <c r="O45" s="7" t="s">
+        <v>150</v>
+      </c>
     </row>
-    <row r="46" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C46" s="5">
         <v>30003030</v>
       </c>
@@ -8570,25 +8945,31 @@
         <v>63</v>
       </c>
       <c r="H46" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="I46" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="I46" s="7" t="s">
+      <c r="J46" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="J46" s="7">
+      <c r="K46" s="7">
         <v>200903</v>
       </c>
-      <c r="K46" s="7">
+      <c r="L46" s="7">
         <v>500</v>
       </c>
-      <c r="L46" s="7" t="s">
+      <c r="M46" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M46" s="7" t="s">
+      <c r="N46" s="7" t="s">
         <v>66</v>
       </c>
+      <c r="O46" s="7" t="s">
+        <v>151</v>
+      </c>
     </row>
-    <row r="47" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C47" s="5">
         <v>30003040</v>
       </c>
@@ -8605,25 +8986,31 @@
         <v>104</v>
       </c>
       <c r="H47" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I47" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="I47" s="7" t="s">
+      <c r="J47" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="J47" s="7">
+      <c r="K47" s="7">
         <v>200903</v>
       </c>
-      <c r="K47" s="7">
+      <c r="L47" s="7">
         <v>400</v>
       </c>
-      <c r="L47" s="7" t="s">
+      <c r="M47" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M47" s="7" t="s">
+      <c r="N47" s="7" t="s">
         <v>111</v>
       </c>
+      <c r="O47" s="7" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="48" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C48" s="5">
         <v>40001000</v>
       </c>
@@ -8640,19 +9027,23 @@
         <v>67</v>
       </c>
       <c r="H48" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="I48" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="I48" s="7" t="s">
+      <c r="J48" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J48" s="7"/>
       <c r="K48" s="7"/>
-      <c r="L48" s="7" t="s">
+      <c r="L48" s="7"/>
+      <c r="M48" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="M48" s="7"/>
+      <c r="N48" s="7"/>
+      <c r="O48" s="7"/>
     </row>
-    <row r="49" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C49" s="5">
         <v>40001010</v>
       </c>
@@ -8669,25 +9060,31 @@
         <v>70</v>
       </c>
       <c r="H49" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="I49" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="I49" s="7" t="s">
+      <c r="J49" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="J49" s="7">
+      <c r="K49" s="7">
         <v>202103</v>
       </c>
-      <c r="K49" s="7">
+      <c r="L49" s="7">
         <v>100</v>
       </c>
-      <c r="L49" s="7" t="s">
+      <c r="M49" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="M49" s="7" t="s">
+      <c r="N49" s="7" t="s">
         <v>34</v>
       </c>
+      <c r="O49" s="7" t="s">
+        <v>144</v>
+      </c>
     </row>
-    <row r="50" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C50" s="5">
         <v>40001020</v>
       </c>
@@ -8704,25 +9101,31 @@
         <v>72</v>
       </c>
       <c r="H50" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I50" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="I50" s="7" t="s">
+      <c r="J50" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="J50" s="7">
+      <c r="K50" s="7">
         <v>201003</v>
       </c>
-      <c r="K50" s="7">
+      <c r="L50" s="7">
         <v>300</v>
       </c>
-      <c r="L50" s="7" t="s">
+      <c r="M50" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="M50" s="7" t="s">
+      <c r="N50" s="7" t="s">
         <v>38</v>
       </c>
+      <c r="O50" s="7" t="s">
+        <v>145</v>
+      </c>
     </row>
-    <row r="51" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C51" s="5">
         <v>40001030</v>
       </c>
@@ -8739,25 +9142,31 @@
         <v>75</v>
       </c>
       <c r="H51" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="I51" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I51" s="7" t="s">
+      <c r="J51" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="J51" s="7">
+      <c r="K51" s="7">
         <v>201003</v>
       </c>
-      <c r="K51" s="7">
+      <c r="L51" s="7">
         <v>500</v>
       </c>
-      <c r="L51" s="7" t="s">
+      <c r="M51" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="M51" s="7" t="s">
+      <c r="N51" s="7" t="s">
         <v>42</v>
       </c>
+      <c r="O51" s="7" t="s">
+        <v>146</v>
+      </c>
     </row>
-    <row r="52" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C52" s="5">
         <v>40001040</v>
       </c>
@@ -8774,25 +9183,31 @@
         <v>95</v>
       </c>
       <c r="H52" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="I52" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="I52" s="7" t="s">
+      <c r="J52" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="J52" s="7">
+      <c r="K52" s="7">
         <v>201003</v>
       </c>
-      <c r="K52" s="7">
+      <c r="L52" s="7">
         <v>400</v>
       </c>
-      <c r="L52" s="7" t="s">
+      <c r="M52" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="M52" s="7" t="s">
+      <c r="N52" s="7" t="s">
         <v>112</v>
       </c>
+      <c r="O52" s="7" t="s">
+        <v>152</v>
+      </c>
     </row>
-    <row r="53" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C53" s="5">
         <v>40002000</v>
       </c>
@@ -8809,19 +9224,23 @@
         <v>43</v>
       </c>
       <c r="H53" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="I53" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I53" s="7" t="s">
+      <c r="J53" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J53" s="7"/>
       <c r="K53" s="7"/>
-      <c r="L53" s="7" t="s">
+      <c r="L53" s="7"/>
+      <c r="M53" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M53" s="7"/>
+      <c r="N53" s="7"/>
+      <c r="O53" s="7"/>
     </row>
-    <row r="54" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C54" s="5">
         <v>40002010</v>
       </c>
@@ -8838,25 +9257,31 @@
         <v>78</v>
       </c>
       <c r="H54" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="I54" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="I54" s="7" t="s">
+      <c r="J54" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="J54" s="7">
+      <c r="K54" s="7">
         <v>200403</v>
       </c>
-      <c r="K54" s="7">
+      <c r="L54" s="7">
         <v>200</v>
       </c>
-      <c r="L54" s="7" t="s">
+      <c r="M54" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M54" s="7" t="s">
+      <c r="N54" s="7" t="s">
         <v>48</v>
       </c>
+      <c r="O54" s="7" t="s">
+        <v>147</v>
+      </c>
     </row>
-    <row r="55" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C55" s="5">
         <v>40002020</v>
       </c>
@@ -8873,25 +9298,31 @@
         <v>80</v>
       </c>
       <c r="H55" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I55" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="I55" s="7" t="s">
+      <c r="J55" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="J55" s="7">
+      <c r="K55" s="7">
         <v>202103</v>
       </c>
-      <c r="K55" s="7">
+      <c r="L55" s="7">
         <v>200</v>
       </c>
-      <c r="L55" s="7" t="s">
+      <c r="M55" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M55" s="7" t="s">
+      <c r="N55" s="7" t="s">
         <v>52</v>
       </c>
+      <c r="O55" s="7" t="s">
+        <v>148</v>
+      </c>
     </row>
-    <row r="56" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C56" s="5">
         <v>40002030</v>
       </c>
@@ -8908,25 +9339,31 @@
         <v>98</v>
       </c>
       <c r="H56" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I56" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="I56" s="7" t="s">
+      <c r="J56" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="J56" s="7">
+      <c r="K56" s="7">
         <v>202103</v>
       </c>
-      <c r="K56" s="7">
+      <c r="L56" s="7">
         <v>300</v>
       </c>
-      <c r="L56" s="7" t="s">
+      <c r="M56" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M56" s="7" t="s">
+      <c r="N56" s="7" t="s">
         <v>113</v>
       </c>
+      <c r="O56" s="7" t="s">
+        <v>153</v>
+      </c>
     </row>
-    <row r="57" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C57" s="5">
         <v>40003000</v>
       </c>
@@ -8943,19 +9380,23 @@
         <v>53</v>
       </c>
       <c r="H57" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="I57" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="I57" s="7" t="s">
+      <c r="J57" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J57" s="7"/>
       <c r="K57" s="7"/>
-      <c r="L57" s="7" t="s">
+      <c r="L57" s="7"/>
+      <c r="M57" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M57" s="7"/>
+      <c r="N57" s="7"/>
+      <c r="O57" s="7"/>
     </row>
-    <row r="58" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C58" s="5">
         <v>40003010</v>
       </c>
@@ -8972,25 +9413,31 @@
         <v>83</v>
       </c>
       <c r="H58" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="I58" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="I58" s="7" t="s">
+      <c r="J58" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="J58" s="7">
+      <c r="K58" s="7">
         <v>200203</v>
       </c>
-      <c r="K58" s="7">
+      <c r="L58" s="7">
         <v>200</v>
       </c>
-      <c r="L58" s="7" t="s">
+      <c r="M58" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M58" s="7" t="s">
+      <c r="N58" s="7" t="s">
         <v>58</v>
       </c>
+      <c r="O58" s="7" t="s">
+        <v>149</v>
+      </c>
     </row>
-    <row r="59" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C59" s="5">
         <v>40003020</v>
       </c>
@@ -9007,25 +9454,31 @@
         <v>85</v>
       </c>
       <c r="H59" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="I59" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="I59" s="7" t="s">
+      <c r="J59" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="J59" s="7">
+      <c r="K59" s="7">
         <v>200903</v>
       </c>
-      <c r="K59" s="7">
+      <c r="L59" s="7">
         <v>300</v>
       </c>
-      <c r="L59" s="7" t="s">
+      <c r="M59" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M59" s="7" t="s">
+      <c r="N59" s="7" t="s">
         <v>62</v>
       </c>
+      <c r="O59" s="7" t="s">
+        <v>150</v>
+      </c>
     </row>
-    <row r="60" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C60" s="5">
         <v>40003030</v>
       </c>
@@ -9042,25 +9495,31 @@
         <v>87</v>
       </c>
       <c r="H60" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="I60" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="I60" s="7" t="s">
+      <c r="J60" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="J60" s="7">
+      <c r="K60" s="7">
         <v>200903</v>
       </c>
-      <c r="K60" s="7">
+      <c r="L60" s="7">
         <v>500</v>
       </c>
-      <c r="L60" s="7" t="s">
+      <c r="M60" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M60" s="7" t="s">
+      <c r="N60" s="7" t="s">
         <v>66</v>
       </c>
+      <c r="O60" s="7" t="s">
+        <v>151</v>
+      </c>
     </row>
-    <row r="61" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C61" s="5">
         <v>40003040</v>
       </c>
@@ -9077,63 +9536,69 @@
         <v>99</v>
       </c>
       <c r="H61" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="I61" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I61" s="7" t="s">
+      <c r="J61" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="J61" s="7">
+      <c r="K61" s="7">
         <v>200903</v>
       </c>
-      <c r="K61" s="7">
+      <c r="L61" s="7">
         <v>400</v>
       </c>
-      <c r="L61" s="7" t="s">
+      <c r="M61" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M61" s="7" t="s">
+      <c r="N61" s="7" t="s">
         <v>111</v>
+      </c>
+      <c r="O61" s="7" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="H17" r:id="rId1" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="H13" r:id="rId2" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="H18" r:id="rId3" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="H12" r:id="rId4" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="H31" r:id="rId5" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="H26" r:id="rId6" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="H32" r:id="rId7" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="H27" r:id="rId8" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="H16" r:id="rId9" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="H30" r:id="rId10" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="H11" r:id="rId11" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="H15" r:id="rId12" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="H45" r:id="rId13" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" display="zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="H41" r:id="rId14" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="H46" r:id="rId15" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" display="zhanshi_2_shangyi@zhanshi_2_xiayi@zhanshi_2_xiezi" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="H40" r:id="rId16" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="H44" r:id="rId17" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="H39" r:id="rId18" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="H43" r:id="rId19" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="H25" r:id="rId20" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="H29" r:id="rId21" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="H28" r:id="rId22" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" display="fashi_2_lian@fashi_2_meimao@fashi_2_yanjing" xr:uid="{1B24B811-BDD3-4332-9D9A-FF58A152C7A7}"/>
-    <hyperlink ref="H33" r:id="rId23" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" display="fashi_2_shangyi@fashi_2_xiayi@fashi_2_xiezi" xr:uid="{04792457-C2C3-4D44-AA8D-E30149D17C89}"/>
-    <hyperlink ref="H19" r:id="rId24" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" display="zhanshi_2_pifeng@zhanshi_2_shangyi@zhanshi_2_xiayi@zhanshi_2_xiezi" xr:uid="{F466E03E-42A4-466A-AC1E-A4172081A3EF}"/>
-    <hyperlink ref="H14" r:id="rId25" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" display="zhanshi_2_meimao@zhanshi_2_yanjing@zhanshi_2_lian" xr:uid="{8D34E12A-C32A-457B-951B-E2F21CD4EF02}"/>
-    <hyperlink ref="H42" r:id="rId26" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" display="zhanshi_2_meimao@zhanshi_2_yanjing@zhanshi_2_lian" xr:uid="{0ACBABF6-946B-466A-9770-538241660925}"/>
-    <hyperlink ref="H47" r:id="rId27" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" display="zhanshi_2_pifeng@zhanshi_2_shangyi@zhanshi_2_xiayi@zhanshi_2_xiezi" xr:uid="{4F45886E-0EFF-4B98-9370-1DF68E6F4DAB}"/>
-    <hyperlink ref="H59" r:id="rId28" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{ECF9C4B3-23FF-4414-B8AF-A7C49AF18A24}"/>
-    <hyperlink ref="H54" r:id="rId29" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" xr:uid="{E0747A8C-C932-4262-B115-D865D0440A77}"/>
-    <hyperlink ref="H60" r:id="rId30" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{838A05A8-FED1-48A0-9CE5-0B8492229D7C}"/>
-    <hyperlink ref="H55" r:id="rId31" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" xr:uid="{A1073D3E-DCAD-4F28-8D86-50476586CE55}"/>
-    <hyperlink ref="H58" r:id="rId32" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{6003702D-640E-458D-A55F-4A79C43D9F8B}"/>
-    <hyperlink ref="H53" r:id="rId33" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" xr:uid="{619DC50E-390B-4CE2-90B0-AAA103A6E2EC}"/>
-    <hyperlink ref="H57" r:id="rId34" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" display="Hero_shangyi@Hero_xiashen@Hero_xiezi@Hero_pifu1@@Hero_pifu2" xr:uid="{246269C2-7A50-41F5-8A27-5C5ACC5EE1D7}"/>
-    <hyperlink ref="H56" r:id="rId35" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" display="fashi_2_lian@fashi_2_meimao@fashi_2_yanjing" xr:uid="{5E88E76B-33FF-4E54-9493-B4A3B34AC447}"/>
-    <hyperlink ref="H61" r:id="rId36" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" display="fashi_2_shangyi@fashi_2_xiayi@fashi_2_xiezi" xr:uid="{5D5844AC-22CB-49AF-8038-DF0E026CA1DF}"/>
+    <hyperlink ref="I17" r:id="rId1" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="I13" r:id="rId2" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="I18" r:id="rId3" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="I12" r:id="rId4" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="I31" r:id="rId5" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="I26" r:id="rId6" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="I32" r:id="rId7" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="I27" r:id="rId8" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="I16" r:id="rId9" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="I30" r:id="rId10" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="I11" r:id="rId11" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="I15" r:id="rId12" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="I45" r:id="rId13" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" display="zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="I41" r:id="rId14" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="I46" r:id="rId15" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" display="zhanshi_2_shangyi@zhanshi_2_xiayi@zhanshi_2_xiezi" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="I40" r:id="rId16" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="I44" r:id="rId17" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="I39" r:id="rId18" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="I43" r:id="rId19" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="I25" r:id="rId20" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="I29" r:id="rId21" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="I28" r:id="rId22" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" display="fashi_2_lian@fashi_2_meimao@fashi_2_yanjing" xr:uid="{1B24B811-BDD3-4332-9D9A-FF58A152C7A7}"/>
+    <hyperlink ref="I33" r:id="rId23" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" display="fashi_2_shangyi@fashi_2_xiayi@fashi_2_xiezi" xr:uid="{04792457-C2C3-4D44-AA8D-E30149D17C89}"/>
+    <hyperlink ref="I19" r:id="rId24" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" display="zhanshi_2_pifeng@zhanshi_2_shangyi@zhanshi_2_xiayi@zhanshi_2_xiezi" xr:uid="{F466E03E-42A4-466A-AC1E-A4172081A3EF}"/>
+    <hyperlink ref="I14" r:id="rId25" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" display="zhanshi_2_meimao@zhanshi_2_yanjing@zhanshi_2_lian" xr:uid="{8D34E12A-C32A-457B-951B-E2F21CD4EF02}"/>
+    <hyperlink ref="I42" r:id="rId26" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" display="zhanshi_2_meimao@zhanshi_2_yanjing@zhanshi_2_lian" xr:uid="{0ACBABF6-946B-466A-9770-538241660925}"/>
+    <hyperlink ref="I47" r:id="rId27" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" display="zhanshi_2_pifeng@zhanshi_2_shangyi@zhanshi_2_xiayi@zhanshi_2_xiezi" xr:uid="{4F45886E-0EFF-4B98-9370-1DF68E6F4DAB}"/>
+    <hyperlink ref="I59" r:id="rId28" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{ECF9C4B3-23FF-4414-B8AF-A7C49AF18A24}"/>
+    <hyperlink ref="I54" r:id="rId29" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" xr:uid="{E0747A8C-C932-4262-B115-D865D0440A77}"/>
+    <hyperlink ref="I60" r:id="rId30" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{838A05A8-FED1-48A0-9CE5-0B8492229D7C}"/>
+    <hyperlink ref="I55" r:id="rId31" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" xr:uid="{A1073D3E-DCAD-4F28-8D86-50476586CE55}"/>
+    <hyperlink ref="I58" r:id="rId32" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{6003702D-640E-458D-A55F-4A79C43D9F8B}"/>
+    <hyperlink ref="I53" r:id="rId33" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" xr:uid="{619DC50E-390B-4CE2-90B0-AAA103A6E2EC}"/>
+    <hyperlink ref="I57" r:id="rId34" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" display="Hero_shangyi@Hero_xiashen@Hero_xiezi@Hero_pifu1@@Hero_pifu2" xr:uid="{246269C2-7A50-41F5-8A27-5C5ACC5EE1D7}"/>
+    <hyperlink ref="I56" r:id="rId35" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" display="fashi_2_lian@fashi_2_meimao@fashi_2_yanjing" xr:uid="{5E88E76B-33FF-4E54-9493-B4A3B34AC447}"/>
+    <hyperlink ref="I61" r:id="rId36" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" display="fashi_2_shangyi@fashi_2_xiayi@fashi_2_xiezi" xr:uid="{5D5844AC-22CB-49AF-8038-DF0E026CA1DF}"/>
   </hyperlinks>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/FashionConfig.xlsx
+++ b/Excel/FashionConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC5EDE47-3CE0-4323-9ECE-27BE1FF5C8F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6424666B-3EFC-4002-A973-2D6E4A9BF575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="155">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -7208,7 +7208,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:O61"/>
+  <dimension ref="C1:O75"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="10.875" customWidth="1"/>
@@ -9557,6 +9557,556 @@
         <v>111</v>
       </c>
       <c r="O61" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C62" s="5">
+        <v>50005000</v>
+      </c>
+      <c r="D62" s="5">
+        <v>1</v>
+      </c>
+      <c r="E62" s="6">
+        <v>1</v>
+      </c>
+      <c r="F62" s="7">
+        <v>1001</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H62" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I62" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J62" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K62" s="7"/>
+      <c r="L62" s="7"/>
+      <c r="M62" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="N62" s="7"/>
+      <c r="O62" s="7"/>
+    </row>
+    <row r="63" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C63" s="5">
+        <v>50001010</v>
+      </c>
+      <c r="D63" s="5">
+        <v>1</v>
+      </c>
+      <c r="E63" s="6">
+        <v>1</v>
+      </c>
+      <c r="F63" s="7">
+        <v>1001</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H63" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="I63" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J63" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="K63" s="7">
+        <v>202103</v>
+      </c>
+      <c r="L63" s="7">
+        <v>100</v>
+      </c>
+      <c r="M63" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="N63" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="O63" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C64" s="5">
+        <v>50001020</v>
+      </c>
+      <c r="D64" s="5">
+        <v>1</v>
+      </c>
+      <c r="E64" s="6">
+        <v>1</v>
+      </c>
+      <c r="F64" s="7">
+        <v>1001</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H64" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="I64" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J64" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K64" s="7">
+        <v>201003</v>
+      </c>
+      <c r="L64" s="7">
+        <v>300</v>
+      </c>
+      <c r="M64" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="N64" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="O64" s="7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="65" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C65" s="5">
+        <v>50001030</v>
+      </c>
+      <c r="D65" s="5">
+        <v>1</v>
+      </c>
+      <c r="E65" s="6">
+        <v>1</v>
+      </c>
+      <c r="F65" s="7">
+        <v>1001</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H65" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="I65" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="J65" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K65" s="7">
+        <v>201003</v>
+      </c>
+      <c r="L65" s="7">
+        <v>500</v>
+      </c>
+      <c r="M65" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="N65" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="O65" s="7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="66" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C66" s="5">
+        <v>50001040</v>
+      </c>
+      <c r="D66" s="5">
+        <v>1</v>
+      </c>
+      <c r="E66" s="6">
+        <v>1</v>
+      </c>
+      <c r="F66" s="7">
+        <v>1001</v>
+      </c>
+      <c r="G66" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="H66" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="I66" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="J66" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="K66" s="7">
+        <v>201003</v>
+      </c>
+      <c r="L66" s="7">
+        <v>400</v>
+      </c>
+      <c r="M66" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="N66" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="O66" s="7" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="67" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C67" s="5">
+        <v>50002000</v>
+      </c>
+      <c r="D67" s="5">
+        <v>1</v>
+      </c>
+      <c r="E67" s="6">
+        <v>2</v>
+      </c>
+      <c r="F67" s="6">
+        <v>2001</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H67" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="I67" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J67" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K67" s="7"/>
+      <c r="L67" s="7"/>
+      <c r="M67" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="N67" s="7"/>
+      <c r="O67" s="7"/>
+    </row>
+    <row r="68" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C68" s="5">
+        <v>50002010</v>
+      </c>
+      <c r="D68" s="5">
+        <v>1</v>
+      </c>
+      <c r="E68" s="6">
+        <v>2</v>
+      </c>
+      <c r="F68" s="6">
+        <v>2001</v>
+      </c>
+      <c r="G68" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H68" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="I68" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J68" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K68" s="7">
+        <v>200403</v>
+      </c>
+      <c r="L68" s="7">
+        <v>200</v>
+      </c>
+      <c r="M68" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="N68" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="O68" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="69" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C69" s="5">
+        <v>50002020</v>
+      </c>
+      <c r="D69" s="5">
+        <v>1</v>
+      </c>
+      <c r="E69" s="6">
+        <v>2</v>
+      </c>
+      <c r="F69" s="6">
+        <v>2001</v>
+      </c>
+      <c r="G69" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H69" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="I69" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J69" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K69" s="7">
+        <v>202103</v>
+      </c>
+      <c r="L69" s="7">
+        <v>200</v>
+      </c>
+      <c r="M69" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="N69" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="O69" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="70" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C70" s="5">
+        <v>50002030</v>
+      </c>
+      <c r="D70" s="5">
+        <v>1</v>
+      </c>
+      <c r="E70" s="6">
+        <v>2</v>
+      </c>
+      <c r="F70" s="6">
+        <v>2001</v>
+      </c>
+      <c r="G70" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="H70" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="I70" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="J70" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="K70" s="7">
+        <v>202103</v>
+      </c>
+      <c r="L70" s="7">
+        <v>300</v>
+      </c>
+      <c r="M70" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="N70" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="O70" s="7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="71" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C71" s="5">
+        <v>50003000</v>
+      </c>
+      <c r="D71" s="5">
+        <v>1</v>
+      </c>
+      <c r="E71" s="6">
+        <v>3</v>
+      </c>
+      <c r="F71" s="6">
+        <v>3001</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="I71" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="J71" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K71" s="7"/>
+      <c r="L71" s="7"/>
+      <c r="M71" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="N71" s="7"/>
+      <c r="O71" s="7"/>
+    </row>
+    <row r="72" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C72" s="5">
+        <v>50003010</v>
+      </c>
+      <c r="D72" s="5">
+        <v>1</v>
+      </c>
+      <c r="E72" s="6">
+        <v>3</v>
+      </c>
+      <c r="F72" s="6">
+        <v>3001</v>
+      </c>
+      <c r="G72" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H72" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="I72" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="J72" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K72" s="7">
+        <v>200203</v>
+      </c>
+      <c r="L72" s="7">
+        <v>200</v>
+      </c>
+      <c r="M72" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="N72" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="O72" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="73" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C73" s="5">
+        <v>50003020</v>
+      </c>
+      <c r="D73" s="5">
+        <v>1</v>
+      </c>
+      <c r="E73" s="6">
+        <v>3</v>
+      </c>
+      <c r="F73" s="6">
+        <v>3001</v>
+      </c>
+      <c r="G73" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H73" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="I73" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="J73" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="K73" s="7">
+        <v>200903</v>
+      </c>
+      <c r="L73" s="7">
+        <v>300</v>
+      </c>
+      <c r="M73" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="N73" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="O73" s="7" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="74" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C74" s="5">
+        <v>50003030</v>
+      </c>
+      <c r="D74" s="5">
+        <v>1</v>
+      </c>
+      <c r="E74" s="6">
+        <v>3</v>
+      </c>
+      <c r="F74" s="6">
+        <v>3001</v>
+      </c>
+      <c r="G74" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H74" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="I74" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="J74" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="K74" s="7">
+        <v>200903</v>
+      </c>
+      <c r="L74" s="7">
+        <v>500</v>
+      </c>
+      <c r="M74" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="N74" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="O74" s="7" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="75" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C75" s="5">
+        <v>50003040</v>
+      </c>
+      <c r="D75" s="5">
+        <v>1</v>
+      </c>
+      <c r="E75" s="6">
+        <v>3</v>
+      </c>
+      <c r="F75" s="6">
+        <v>3001</v>
+      </c>
+      <c r="G75" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="H75" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I75" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="J75" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K75" s="7">
+        <v>200903</v>
+      </c>
+      <c r="L75" s="7">
+        <v>400</v>
+      </c>
+      <c r="M75" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="N75" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="O75" s="7" t="s">
         <v>154</v>
       </c>
     </row>
@@ -9599,9 +10149,18 @@
     <hyperlink ref="I57" r:id="rId34" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" display="Hero_shangyi@Hero_xiashen@Hero_xiezi@Hero_pifu1@@Hero_pifu2" xr:uid="{246269C2-7A50-41F5-8A27-5C5ACC5EE1D7}"/>
     <hyperlink ref="I56" r:id="rId35" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" display="fashi_2_lian@fashi_2_meimao@fashi_2_yanjing" xr:uid="{5E88E76B-33FF-4E54-9493-B4A3B34AC447}"/>
     <hyperlink ref="I61" r:id="rId36" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" display="fashi_2_shangyi@fashi_2_xiayi@fashi_2_xiezi" xr:uid="{5D5844AC-22CB-49AF-8038-DF0E026CA1DF}"/>
+    <hyperlink ref="I73" r:id="rId37" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{630BD411-A999-4490-B7A6-50DD58B3DC53}"/>
+    <hyperlink ref="I69" r:id="rId38" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" xr:uid="{0372364C-F039-44FE-817C-EA2ACD5BA743}"/>
+    <hyperlink ref="I74" r:id="rId39" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{015FDE7D-BD4E-4C06-A6FF-B21CFAC1DE51}"/>
+    <hyperlink ref="I68" r:id="rId40" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" xr:uid="{B679A316-C2D4-4499-9125-05BC40DA1CC0}"/>
+    <hyperlink ref="I72" r:id="rId41" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{CD084000-A06A-4D48-BB8B-47AFBB9F5A6A}"/>
+    <hyperlink ref="I67" r:id="rId42" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" xr:uid="{2042CB79-C838-44A8-960D-436C6060DC5E}"/>
+    <hyperlink ref="I71" r:id="rId43" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" xr:uid="{B9231A86-4813-4C01-BD59-DA549147421D}"/>
+    <hyperlink ref="I75" r:id="rId44" tooltip="mailto:zhanshi_1_pifeng@zhanshi_1_shangyi@zhanshi_1_xiayi@zhanshi_1_xiezi" display="zhanshi_2_pifeng@zhanshi_2_shangyi@zhanshi_2_xiayi@zhanshi_2_xiezi" xr:uid="{642FA238-592A-4D48-A9F4-E6553BBFF586}"/>
+    <hyperlink ref="I70" r:id="rId45" tooltip="mailto:zhanshi_1_meimao@zhanshi_1_yanjing@zhanshi_1_lian" display="zhanshi_2_meimao@zhanshi_2_yanjing@zhanshi_2_lian" xr:uid="{8FA63BAD-663A-435E-83E9-09889194F12A}"/>
   </hyperlinks>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId37"/>
+  <legacyDrawing r:id="rId46"/>
 </worksheet>
 </file>
--- a/Excel/FashionConfig.xlsx
+++ b/Excel/FashionConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6424666B-3EFC-4002-A973-2D6E4A9BF575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{447957B3-3C0C-4866-AC86-A6E878BCE0F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9562,7 +9562,7 @@
     </row>
     <row r="62" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C62" s="5">
-        <v>50005000</v>
+        <v>50001000</v>
       </c>
       <c r="D62" s="5">
         <v>1</v>

--- a/Excel/FashionConfig.xlsx
+++ b/Excel/FashionConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{447957B3-3C0C-4866-AC86-A6E878BCE0F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A4E1DE5-FD79-4162-BB15-E9288F560007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FashionProto" sheetId="1" r:id="rId1"/>
@@ -9565,7 +9565,7 @@
         <v>50001000</v>
       </c>
       <c r="D62" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E62" s="6">
         <v>1</v>
@@ -9598,7 +9598,7 @@
         <v>50001010</v>
       </c>
       <c r="D63" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E63" s="6">
         <v>1</v>
@@ -9639,7 +9639,7 @@
         <v>50001020</v>
       </c>
       <c r="D64" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E64" s="6">
         <v>1</v>
@@ -9680,7 +9680,7 @@
         <v>50001030</v>
       </c>
       <c r="D65" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E65" s="6">
         <v>1</v>
@@ -9721,7 +9721,7 @@
         <v>50001040</v>
       </c>
       <c r="D66" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E66" s="6">
         <v>1</v>
@@ -9762,7 +9762,7 @@
         <v>50002000</v>
       </c>
       <c r="D67" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E67" s="6">
         <v>2</v>
@@ -9795,7 +9795,7 @@
         <v>50002010</v>
       </c>
       <c r="D68" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E68" s="6">
         <v>2</v>
@@ -9836,7 +9836,7 @@
         <v>50002020</v>
       </c>
       <c r="D69" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E69" s="6">
         <v>2</v>
@@ -9877,7 +9877,7 @@
         <v>50002030</v>
       </c>
       <c r="D70" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E70" s="6">
         <v>2</v>
@@ -9918,7 +9918,7 @@
         <v>50003000</v>
       </c>
       <c r="D71" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E71" s="6">
         <v>3</v>
@@ -9951,7 +9951,7 @@
         <v>50003010</v>
       </c>
       <c r="D72" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E72" s="6">
         <v>3</v>
@@ -9992,7 +9992,7 @@
         <v>50003020</v>
       </c>
       <c r="D73" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E73" s="6">
         <v>3</v>
@@ -10033,7 +10033,7 @@
         <v>50003030</v>
       </c>
       <c r="D74" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E74" s="6">
         <v>3</v>
@@ -10074,7 +10074,7 @@
         <v>50003040</v>
       </c>
       <c r="D75" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E75" s="6">
         <v>3</v>
